--- a/artfynd/A 18784-2024 artfynd.xlsx
+++ b/artfynd/A 18784-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY127"/>
+  <dimension ref="A1:AZ127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657503</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114769154</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640993</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115659817</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657599</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114769153</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115024803</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115024805</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115024810</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1654,6 +1704,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115024806</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1760,6 +1815,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104748950</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1870,6 +1930,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104748985</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1971,6 +2036,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114653800</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2078,6 +2148,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114776389</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2184,6 +2259,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773547</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2294,6 +2374,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104748977</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2404,6 +2489,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104748984</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2519,6 +2609,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104748988</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2622,6 +2717,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773368</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2725,6 +2825,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773373</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2831,6 +2936,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773512</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2937,6 +3047,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773537</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3043,6 +3158,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773543</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3149,6 +3269,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773546</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3255,6 +3380,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773554</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3361,6 +3491,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114775570</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3467,6 +3602,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114775585</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3573,6 +3713,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114775601</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3679,6 +3824,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114775603</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3785,6 +3935,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114775625</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3891,6 +4046,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114775810</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3997,6 +4157,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114776119</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4103,6 +4268,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114776127</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4209,6 +4379,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114776131</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4315,6 +4490,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114776139</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4421,6 +4601,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114776144</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4528,6 +4713,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114776391</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4635,6 +4825,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114776396</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4745,6 +4940,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104748967</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4855,6 +5055,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104748969</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4965,6 +5170,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104748978</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5075,6 +5285,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104748983</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5181,6 +5396,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773536</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5287,6 +5507,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773553</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5393,6 +5618,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114775575</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5499,6 +5729,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114775583</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5605,6 +5840,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114775584</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5711,6 +5951,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114776130</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5818,6 +6063,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114776390</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5926,6 +6176,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773367</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6032,6 +6287,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773511</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6138,6 +6398,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773542</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6239,6 +6504,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114653852</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6347,6 +6617,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773372</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6453,6 +6728,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773510</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6559,6 +6839,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114775811</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6665,6 +6950,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114776121</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6773,6 +7063,11 @@
       <c r="AY59" t="inlineStr">
         <is>
           <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104748970</t>
         </is>
       </c>
     </row>
@@ -6876,6 +7171,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114653851</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6982,6 +7282,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773540</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7088,6 +7393,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773548</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7194,6 +7504,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114775572</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7300,6 +7615,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114775607</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7406,6 +7726,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114776118</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7512,6 +7837,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114776142</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7619,6 +7949,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114776400</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7720,6 +8055,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114653849</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7828,6 +8168,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773374</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7934,6 +8279,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773509</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8040,6 +8390,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114773549</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8137,6 +8492,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657404</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8234,6 +8594,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640991</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8340,6 +8705,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114654633</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8446,6 +8816,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114654634</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8547,6 +8922,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657304</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8648,6 +9028,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657305</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8749,6 +9134,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657306</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8850,6 +9240,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657307</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8951,6 +9346,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657308</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9052,6 +9452,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657400</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9153,6 +9558,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657401</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9254,6 +9664,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657402</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9351,6 +9766,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640626</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9448,6 +9868,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640988</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9545,6 +9970,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640992</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9646,6 +10076,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104748980</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9747,6 +10182,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104748981</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9848,6 +10288,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104748989</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9949,6 +10394,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104748990</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10046,6 +10496,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657479</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10143,6 +10598,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657480</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10241,6 +10701,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768021</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10339,6 +10804,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768025</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10437,6 +10907,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768042</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10535,6 +11010,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768043</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10633,6 +11113,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768044</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10731,6 +11216,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768050</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10829,6 +11319,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768051</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10927,6 +11422,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768052</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11025,6 +11525,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768053</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11123,6 +11628,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768054</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11221,6 +11731,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768055</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11319,6 +11834,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768056</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11417,6 +11937,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768057</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11515,6 +12040,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768061</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11613,6 +12143,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768062</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11711,6 +12246,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768063</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11809,6 +12349,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768064</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11907,6 +12452,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768065</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12005,6 +12555,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768066</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12103,6 +12658,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768067</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12201,6 +12761,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114768193</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12303,6 +12868,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114775619</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12404,6 +12974,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657508</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12523,6 +13098,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657509</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12624,6 +13204,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657510</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12725,6 +13310,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657511</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12826,6 +13416,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657512</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12927,6 +13522,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657513</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13028,6 +13628,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657572</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13129,6 +13734,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657573</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13230,6 +13840,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657574</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13331,6 +13946,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657575</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13432,6 +14052,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657576</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13533,6 +14158,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657577</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13634,8 +14264,141 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114657578</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>